--- a/output/weekly_revenue_report_2026-07-03.xlsx
+++ b/output/weekly_revenue_report_2026-07-03.xlsx
@@ -456,7 +456,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>5926614.38</t>
+          <t>4806197.93</t>
         </is>
       </c>
     </row>
@@ -471,7 +471,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4114247.28</t>
+          <t>3097010.03</t>
         </is>
       </c>
     </row>
